--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:48</t>
+    <t xml:space="preserve">2026-09-09 22:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:36</t>
+    <t xml:space="preserve">2026-09-12 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
@@ -36,159 +36,159 @@
     <t xml:space="preserve">Metropolitana</t>
   </si>
   <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Pedro</t>
   </si>
   <si>
+    <t xml:space="preserve">Isla de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San José de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Hurtado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lampa</t>
   </si>
   <si>
+    <t xml:space="preserve">Talagante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Buin</t>
   </si>
   <si>
-    <t xml:space="preserve">Padre Hurtado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Maipo</t>
+    <t xml:space="preserve">Tiltil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curacaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Monte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alhué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
   </si>
   <si>
     <t xml:space="preserve">San Miguel</t>
   </si>
   <si>
-    <t xml:space="preserve">Curacaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San José de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cisterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talagante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alhué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Monte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
     <t xml:space="preserve">La Florida</t>
   </si>
   <si>
     <t xml:space="preserve">Peñaflor</t>
   </si>
   <si>
-    <t xml:space="preserve">Huechuraba</t>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bernardo</t>
   </si>
   <si>
     <t xml:space="preserve">Macul</t>
   </si>
   <si>
-    <t xml:space="preserve">San Joaquín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitacura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Bernardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina</t>
+    <t xml:space="preserve">Independencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recoleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Espejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta Normal</t>
   </si>
   <si>
     <t xml:space="preserve">Pudahuel</t>
   </si>
   <si>
-    <t xml:space="preserve">Quilicura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Pintana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puente Alto</t>
-  </si>
-  <si>
     <t xml:space="preserve">Renca</t>
   </si>
   <si>
-    <t xml:space="preserve">San Ramón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiltil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Espejo</t>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Prado</t>
   </si>
   <si>
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Bosque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedro Aguirre Cerda</t>
-  </si>
-  <si>
     <t xml:space="preserve">Estación Central</t>
   </si>
   <si>
-    <t xml:space="preserve">Quinta Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Prado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recoleta</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calera de Tango</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:52</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -631,13 +631,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>13505</v>
+        <v>13123</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14.24</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="3">
@@ -648,13 +648,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>13302</v>
+        <v>13505</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12.33</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="4">
@@ -665,13 +665,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>13402</v>
+        <v>13603</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9.2</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="5">
@@ -682,13 +682,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>13604</v>
+        <v>13115</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9.14</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="6">
@@ -699,13 +699,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>13603</v>
+        <v>13202</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7.82</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="7">
@@ -716,13 +716,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>13130</v>
+        <v>13203</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6.08</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="8">
@@ -733,13 +733,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>13503</v>
+        <v>13114</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6.04</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="9">
@@ -750,13 +750,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>13404</v>
+        <v>13604</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5.82</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="10">
@@ -767,13 +767,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>13120</v>
+        <v>13132</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>5.63</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="11">
@@ -784,13 +784,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>13203</v>
+        <v>13504</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4.17</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="12">
@@ -801,13 +801,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>13504</v>
+        <v>13302</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3.79</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="13">
@@ -818,13 +818,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>13123</v>
+        <v>13601</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3.64</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="14">
@@ -835,13 +835,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>13301</v>
+        <v>13404</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3.55</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="15">
@@ -852,13 +852,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>13115</v>
+        <v>13120</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.69</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="16">
@@ -869,13 +869,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>13109</v>
+        <v>13402</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.63</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="17">
@@ -886,13 +886,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>13114</v>
+        <v>13303</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.34</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="18">
@@ -903,13 +903,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>13601</v>
+        <v>13301</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="19">
@@ -920,13 +920,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>13502</v>
+        <v>13107</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.03</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="20">
@@ -937,13 +937,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>13602</v>
+        <v>13113</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.97</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="21">
@@ -954,13 +954,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>13501</v>
+        <v>13503</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.96</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="22">
@@ -971,13 +971,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>13202</v>
+        <v>13501</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.36</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="23">
@@ -988,13 +988,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>13102</v>
+        <v>13109</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-1.52</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="24">
@@ -1005,13 +1005,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>13110</v>
+        <v>13602</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-2</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="25">
@@ -1022,13 +1022,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>13605</v>
+        <v>13102</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-2.48</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="26">
@@ -1039,13 +1039,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>13107</v>
+        <v>13502</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-2.86</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="27">
@@ -1056,13 +1056,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>13118</v>
+        <v>13111</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-3.17</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="28">
@@ -1073,13 +1073,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>13129</v>
+        <v>13130</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-3.42</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="29">
@@ -1090,13 +1090,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>13132</v>
+        <v>13110</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-3.8</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="30">
@@ -1107,13 +1107,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>13401</v>
+        <v>13605</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-3.89</v>
+        <v>-0.81</v>
       </c>
     </row>
     <row r="31">
@@ -1124,13 +1124,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>13113</v>
+        <v>13122</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-4.79</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="32">
@@ -1141,13 +1141,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>13124</v>
+        <v>13121</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-6.07</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="33">
@@ -1158,13 +1158,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>13125</v>
+        <v>13129</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-6.13</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="34">
@@ -1175,13 +1175,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>13122</v>
+        <v>13125</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-6.33</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="35">
@@ -1192,13 +1192,13 @@
         <v>39</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>13111</v>
+        <v>13401</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-6.48</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="36">
@@ -1209,13 +1209,13 @@
         <v>40</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>13103</v>
+        <v>13118</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-6.59</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="37">
@@ -1226,13 +1226,13 @@
         <v>41</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>13112</v>
+        <v>13108</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-6.6</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="38">
@@ -1243,13 +1243,13 @@
         <v>42</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>13201</v>
+        <v>13127</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-6.6</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="39">
@@ -1260,13 +1260,13 @@
         <v>43</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>13128</v>
+        <v>13112</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-6.88</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="40">
@@ -1277,13 +1277,13 @@
         <v>44</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>13131</v>
+        <v>13201</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-6.96</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="41">
@@ -1294,13 +1294,13 @@
         <v>45</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>13303</v>
+        <v>13103</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-7.54</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="42">
@@ -1311,13 +1311,13 @@
         <v>46</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>13116</v>
+        <v>13101</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>-7.54</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="43">
@@ -1328,13 +1328,13 @@
         <v>47</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13104</v>
+        <v>13119</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>-7.65</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="44">
@@ -1345,13 +1345,13 @@
         <v>48</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>13119</v>
+        <v>13116</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>-7.66</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="45">
@@ -1362,13 +1362,13 @@
         <v>49</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>13105</v>
+        <v>13131</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>-7.68</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="46">
@@ -1379,13 +1379,13 @@
         <v>50</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>13101</v>
+        <v>13126</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>-7.92</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="47">
@@ -1396,13 +1396,13 @@
         <v>51</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>13121</v>
+        <v>13124</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>-7.94</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="48">
@@ -1413,13 +1413,13 @@
         <v>52</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>13106</v>
+        <v>13128</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>-7.94</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="49">
@@ -1430,13 +1430,13 @@
         <v>53</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>13126</v>
+        <v>13105</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>-7.95</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="50">
@@ -1453,7 +1453,7 @@
         <v>2023</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>-9.04</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="51">
@@ -1464,13 +1464,13 @@
         <v>55</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>13108</v>
+        <v>13104</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>-9.2</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="52">
@@ -1481,13 +1481,13 @@
         <v>56</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>13127</v>
+        <v>13106</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>-9.99</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="53">
@@ -1504,7 +1504,7 @@
         <v>2023</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>-27.95</v>
+        <v>-5.42</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -637,7 +637,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3.8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.71</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +671,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.98</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="5">
@@ -688,7 +688,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2.76</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="6">
@@ -705,7 +705,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.65</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="7">
@@ -722,7 +722,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.49</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="8">
@@ -739,7 +739,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.46</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="9">
@@ -756,7 +756,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.35</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="10">
@@ -773,7 +773,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.33</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="11">
@@ -790,7 +790,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.31</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="12">
@@ -807,7 +807,7 @@
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.31</v>
+        <v>13.08</v>
       </c>
     </row>
     <row r="13">
@@ -824,7 +824,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.27</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="14">
@@ -841,7 +841,7 @@
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.23</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="15">
@@ -858,7 +858,7 @@
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.99</v>
+        <v>9.86</v>
       </c>
     </row>
     <row r="16">
@@ -875,7 +875,7 @@
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.97</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="17">
@@ -892,7 +892,7 @@
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.89</v>
+        <v>8.95</v>
       </c>
     </row>
     <row r="18">
@@ -909,7 +909,7 @@
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.64</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="19">
@@ -926,7 +926,7 @@
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="20">
@@ -943,7 +943,7 @@
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.14</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="21">
@@ -960,7 +960,7 @@
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.07</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="22">
@@ -977,7 +977,7 @@
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.1</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="23">
@@ -994,7 +994,7 @@
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.17</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="24">
@@ -1011,7 +1011,7 @@
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.35</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="25">
@@ -1028,7 +1028,7 @@
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.51</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="26">
@@ -1045,7 +1045,7 @@
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.6</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="27">
@@ -1062,7 +1062,7 @@
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.65</v>
+        <v>-6.47</v>
       </c>
     </row>
     <row r="28">
@@ -1079,7 +1079,7 @@
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-0.67</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="29">
@@ -1096,7 +1096,7 @@
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-0.79</v>
+        <v>-7.94</v>
       </c>
     </row>
     <row r="30">
@@ -1113,7 +1113,7 @@
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-0.81</v>
+        <v>-8.09</v>
       </c>
     </row>
     <row r="31">
@@ -1130,7 +1130,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-0.86</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="32">
@@ -1147,7 +1147,7 @@
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-0.87</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="33">
@@ -1164,7 +1164,7 @@
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-1.1</v>
+        <v>-10.98</v>
       </c>
     </row>
     <row r="34">
@@ -1181,7 +1181,7 @@
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-1.29</v>
+        <v>-12.93</v>
       </c>
     </row>
     <row r="35">
@@ -1198,7 +1198,7 @@
         <v>2023</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-1.38</v>
+        <v>-13.8</v>
       </c>
     </row>
     <row r="36">
@@ -1215,7 +1215,7 @@
         <v>2023</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-1.39</v>
+        <v>-13.89</v>
       </c>
     </row>
     <row r="37">
@@ -1232,7 +1232,7 @@
         <v>2023</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-1.41</v>
+        <v>-14.09</v>
       </c>
     </row>
     <row r="38">
@@ -1249,7 +1249,7 @@
         <v>2023</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-1.44</v>
+        <v>-14.42</v>
       </c>
     </row>
     <row r="39">
@@ -1266,7 +1266,7 @@
         <v>2023</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-1.46</v>
+        <v>-14.57</v>
       </c>
     </row>
     <row r="40">
@@ -1283,7 +1283,7 @@
         <v>2023</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-1.49</v>
+        <v>-14.9</v>
       </c>
     </row>
     <row r="41">
@@ -1300,7 +1300,7 @@
         <v>2023</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-1.62</v>
+        <v>-16.23</v>
       </c>
     </row>
     <row r="42">
@@ -1317,7 +1317,7 @@
         <v>2023</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>-1.63</v>
+        <v>-16.25</v>
       </c>
     </row>
     <row r="43">
@@ -1334,7 +1334,7 @@
         <v>2023</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>-1.64</v>
+        <v>-16.38</v>
       </c>
     </row>
     <row r="44">
@@ -1351,7 +1351,7 @@
         <v>2023</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>-1.74</v>
+        <v>-17.44</v>
       </c>
     </row>
     <row r="45">
@@ -1368,7 +1368,7 @@
         <v>2023</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>-1.76</v>
+        <v>-17.64</v>
       </c>
     </row>
     <row r="46">
@@ -1385,7 +1385,7 @@
         <v>2023</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>-1.84</v>
+        <v>-18.42</v>
       </c>
     </row>
     <row r="47">
@@ -1402,7 +1402,7 @@
         <v>2023</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>-1.85</v>
+        <v>-18.51</v>
       </c>
     </row>
     <row r="48">
@@ -1419,7 +1419,7 @@
         <v>2023</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>-1.91</v>
+        <v>-19.07</v>
       </c>
     </row>
     <row r="49">
@@ -1436,7 +1436,7 @@
         <v>2023</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>-2.01</v>
+        <v>-20.05</v>
       </c>
     </row>
     <row r="50">
@@ -1453,7 +1453,7 @@
         <v>2023</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>-2.06</v>
+        <v>-20.63</v>
       </c>
     </row>
     <row r="51">
@@ -1470,7 +1470,7 @@
         <v>2023</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>-2.52</v>
+        <v>-25.18</v>
       </c>
     </row>
     <row r="52">
@@ -1487,7 +1487,7 @@
         <v>2023</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>-3.11</v>
+        <v>-31.13</v>
       </c>
     </row>
     <row r="53">
@@ -1504,7 +1504,7 @@
         <v>2023</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>-5.42</v>
+        <v>-54.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-10-01 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:59</t>
+    <t xml:space="preserve">2026-10-02 13:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:33</t>
+    <t xml:space="preserve">2026-10-05 08:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
